--- a/tc2.xlsx
+++ b/tc2.xlsx
@@ -425,33 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>story_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>user_story_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
         </is>
       </c>
     </row>
@@ -468,7 +473,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>As a user, I want to generate a valid EDI 270 inquiry file so that eligibility requests can be processed successfully.</t>
+          <t>As a user</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -481,31 +486,17 @@
           <t>Draft</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>US-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Validate EDI 271 Response</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>As a user, I want to validate the EDI 271 response file so that delinquency status details are correctly received.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Draft</t>
         </is>
       </c>
     </row>
